--- a/Result/profitability/2348.xlsx
+++ b/Result/profitability/2348.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>1.505</v>
+        <v>1.135</v>
       </c>
       <c r="N2" t="n">
-        <v>30.305</v>
+        <v>26.45375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>1.00625</v>
+        <v>0.97</v>
       </c>
       <c r="N3" t="n">
-        <v>23.51375</v>
+        <v>24.75625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8225</v>
+        <v>0.6425000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>21.80125</v>
+        <v>18.92875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.51</v>
       </c>
       <c r="M5" t="n">
-        <v>0.465</v>
+        <v>0.46625</v>
       </c>
       <c r="N5" t="n">
-        <v>15.9875</v>
+        <v>15.4575</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3412500000000001</v>
+        <v>0.41</v>
       </c>
       <c r="N6" t="n">
-        <v>12.53</v>
+        <v>11.41625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.25</v>
+        <v>-0.03999999999999994</v>
       </c>
       <c r="N7" t="n">
-        <v>8.66</v>
+        <v>7.4725</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.46</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2112499999999999</v>
+        <v>-0.1174999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>4.54375</v>
+        <v>4.09625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>-0.37</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.32125</v>
+        <v>-0.3212499999999999</v>
       </c>
       <c r="N10" t="n">
         <v>1.26</v>
@@ -1899,7 +1899,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3975</v>
+        <v>-0.3974999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>1.4975</v>
@@ -2026,7 +2026,7 @@
         <v>-0.27</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3675</v>
+        <v>-0.3674999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>1.57625</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2348</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1808</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1364</v>
+      </c>
+      <c r="E75" t="n">
+        <v>444</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="G75" t="n">
+        <v>269</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.90%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>269</v>
+      </c>
+      <c r="K75" t="n">
+        <v>193</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.6225</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4.6875</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.580000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1273115220483643</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.01111111111111107</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.240000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.147324530924253</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
